--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376438</v>
+        <v>124376483</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467340</v>
+        <v>467331</v>
       </c>
       <c r="R2" t="n">
-        <v>6721127</v>
+        <v>6721130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376483</v>
+        <v>124376501</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467331</v>
+        <v>467318</v>
       </c>
       <c r="R3" t="n">
-        <v>6721130</v>
+        <v>6721132</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376474</v>
+        <v>124376453</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467337</v>
+        <v>467327</v>
       </c>
       <c r="R4" t="n">
-        <v>6721115</v>
+        <v>6721126</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376453</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467327</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721126</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376501</v>
+        <v>124376474</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467318</v>
+        <v>467337</v>
       </c>
       <c r="R6" t="n">
-        <v>6721132</v>
+        <v>6721115</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376483</v>
+        <v>124376453</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467331</v>
+        <v>467327</v>
       </c>
       <c r="R2" t="n">
-        <v>6721130</v>
+        <v>6721126</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376501</v>
+        <v>124376438</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467318</v>
+        <v>467340</v>
       </c>
       <c r="R3" t="n">
-        <v>6721132</v>
+        <v>6721127</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376453</v>
+        <v>124376483</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +917,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467327</v>
+        <v>467331</v>
       </c>
       <c r="R4" t="n">
-        <v>6721126</v>
+        <v>6721130</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376474</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1023,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467337</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721115</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376474</v>
+        <v>124376501</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467337</v>
+        <v>467318</v>
       </c>
       <c r="R6" t="n">
-        <v>6721115</v>
+        <v>6721132</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376453</v>
+        <v>124376483</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467327</v>
+        <v>467331</v>
       </c>
       <c r="R2" t="n">
-        <v>6721126</v>
+        <v>6721130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376438</v>
+        <v>124376474</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467340</v>
+        <v>467337</v>
       </c>
       <c r="R3" t="n">
-        <v>6721127</v>
+        <v>6721115</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -905,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376483</v>
+        <v>124376501</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467331</v>
+        <v>467318</v>
       </c>
       <c r="R4" t="n">
-        <v>6721130</v>
+        <v>6721132</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376474</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,30 +1005,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467337</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721115</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376501</v>
+        <v>124376453</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1120,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467318</v>
+        <v>467327</v>
       </c>
       <c r="R6" t="n">
-        <v>6721132</v>
+        <v>6721126</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376483</v>
+        <v>124376474</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467331</v>
+        <v>467337</v>
       </c>
       <c r="R2" t="n">
-        <v>6721130</v>
+        <v>6721115</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376474</v>
+        <v>124376453</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467337</v>
+        <v>467327</v>
       </c>
       <c r="R3" t="n">
-        <v>6721115</v>
+        <v>6721126</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1108,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376453</v>
+        <v>124376483</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,39 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467327</v>
+        <v>467331</v>
       </c>
       <c r="R6" t="n">
-        <v>6721126</v>
+        <v>6721130</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376474</v>
+        <v>124376483</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467337</v>
+        <v>467331</v>
       </c>
       <c r="R2" t="n">
-        <v>6721115</v>
+        <v>6721130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376453</v>
+        <v>124376438</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467327</v>
+        <v>467340</v>
       </c>
       <c r="R3" t="n">
-        <v>6721126</v>
+        <v>6721127</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376501</v>
+        <v>124376474</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467318</v>
+        <v>467337</v>
       </c>
       <c r="R4" t="n">
-        <v>6721132</v>
+        <v>6721115</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376501</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467318</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721132</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376483</v>
+        <v>124376453</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1120,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467331</v>
+        <v>467327</v>
       </c>
       <c r="R6" t="n">
-        <v>6721130</v>
+        <v>6721126</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376438</v>
+        <v>124376453</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467340</v>
+        <v>467327</v>
       </c>
       <c r="R3" t="n">
-        <v>6721127</v>
+        <v>6721126</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376501</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,30 +1014,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467318</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721132</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376453</v>
+        <v>124376501</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,39 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467327</v>
+        <v>467318</v>
       </c>
       <c r="R6" t="n">
-        <v>6721126</v>
+        <v>6721132</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376483</v>
+        <v>124376453</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467331</v>
+        <v>467327</v>
       </c>
       <c r="R2" t="n">
-        <v>6721130</v>
+        <v>6721126</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376453</v>
+        <v>124376501</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467327</v>
+        <v>467318</v>
       </c>
       <c r="R3" t="n">
-        <v>6721126</v>
+        <v>6721132</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376474</v>
+        <v>124376438</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467337</v>
+        <v>467340</v>
       </c>
       <c r="R4" t="n">
-        <v>6721115</v>
+        <v>6721127</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376474</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1023,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467337</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721115</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376501</v>
+        <v>124376483</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467318</v>
+        <v>467331</v>
       </c>
       <c r="R6" t="n">
-        <v>6721132</v>
+        <v>6721130</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376453</v>
+        <v>124376438</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467327</v>
+        <v>467340</v>
       </c>
       <c r="R2" t="n">
-        <v>6721126</v>
+        <v>6721127</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376438</v>
+        <v>124376453</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -931,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467340</v>
+        <v>467327</v>
       </c>
       <c r="R4" t="n">
-        <v>6721127</v>
+        <v>6721126</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376438</v>
+        <v>124376483</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467340</v>
+        <v>467331</v>
       </c>
       <c r="R2" t="n">
-        <v>6721127</v>
+        <v>6721130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376501</v>
+        <v>124376474</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467318</v>
+        <v>467337</v>
       </c>
       <c r="R3" t="n">
-        <v>6721132</v>
+        <v>6721115</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1011,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376474</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,30 +1014,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467337</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721115</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376483</v>
+        <v>124376501</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467331</v>
+        <v>467318</v>
       </c>
       <c r="R6" t="n">
-        <v>6721130</v>
+        <v>6721132</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376483</v>
+        <v>124376438</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467331</v>
+        <v>467340</v>
       </c>
       <c r="R2" t="n">
-        <v>6721130</v>
+        <v>6721127</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376474</v>
+        <v>124376501</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467337</v>
+        <v>467318</v>
       </c>
       <c r="R3" t="n">
-        <v>6721115</v>
+        <v>6721132</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376453</v>
+        <v>124376483</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467327</v>
+        <v>467331</v>
       </c>
       <c r="R4" t="n">
-        <v>6721126</v>
+        <v>6721130</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376474</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467337</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721115</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376501</v>
+        <v>124376453</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1120,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467318</v>
+        <v>467327</v>
       </c>
       <c r="R6" t="n">
-        <v>6721132</v>
+        <v>6721126</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376438</v>
+        <v>124376501</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467340</v>
+        <v>467318</v>
       </c>
       <c r="R2" t="n">
-        <v>6721127</v>
+        <v>6721132</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376501</v>
+        <v>124376483</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467318</v>
+        <v>467331</v>
       </c>
       <c r="R3" t="n">
-        <v>6721132</v>
+        <v>6721130</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376483</v>
+        <v>124376453</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467331</v>
+        <v>467327</v>
       </c>
       <c r="R4" t="n">
-        <v>6721130</v>
+        <v>6721126</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376474</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,30 +1014,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467337</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721115</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376453</v>
+        <v>124376474</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,39 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467327</v>
+        <v>467337</v>
       </c>
       <c r="R6" t="n">
-        <v>6721126</v>
+        <v>6721115</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376483</v>
+        <v>124376474</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467331</v>
+        <v>467337</v>
       </c>
       <c r="R3" t="n">
-        <v>6721130</v>
+        <v>6721115</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376453</v>
+        <v>124376483</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467327</v>
+        <v>467331</v>
       </c>
       <c r="R4" t="n">
-        <v>6721126</v>
+        <v>6721130</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376453</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1037,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467327</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721126</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376474</v>
+        <v>124376438</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1120,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467337</v>
+        <v>467340</v>
       </c>
       <c r="R6" t="n">
-        <v>6721115</v>
+        <v>6721127</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376501</v>
+        <v>124376483</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467318</v>
+        <v>467331</v>
       </c>
       <c r="R2" t="n">
-        <v>6721132</v>
+        <v>6721130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376474</v>
+        <v>124376501</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467337</v>
+        <v>467318</v>
       </c>
       <c r="R3" t="n">
-        <v>6721115</v>
+        <v>6721132</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376483</v>
+        <v>124376453</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467331</v>
+        <v>467327</v>
       </c>
       <c r="R4" t="n">
-        <v>6721130</v>
+        <v>6721126</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376453</v>
+        <v>124376438</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1028,7 +1037,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1045,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467327</v>
+        <v>467340</v>
       </c>
       <c r="R5" t="n">
-        <v>6721126</v>
+        <v>6721127</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376438</v>
+        <v>124376474</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,39 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467340</v>
+        <v>467337</v>
       </c>
       <c r="R6" t="n">
-        <v>6721127</v>
+        <v>6721115</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376483</v>
+        <v>124376474</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467331</v>
+        <v>467337</v>
       </c>
       <c r="R2" t="n">
-        <v>6721130</v>
+        <v>6721115</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376501</v>
+        <v>124376483</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467318</v>
+        <v>467331</v>
       </c>
       <c r="R3" t="n">
-        <v>6721132</v>
+        <v>6721130</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376453</v>
+        <v>124376438</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467327</v>
+        <v>467340</v>
       </c>
       <c r="R4" t="n">
-        <v>6721126</v>
+        <v>6721127</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376438</v>
+        <v>124376453</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,7 +1017,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467340</v>
+        <v>467327</v>
       </c>
       <c r="R5" t="n">
-        <v>6721127</v>
+        <v>6721126</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,37 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376474</v>
+        <v>124376501</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467337</v>
+        <v>467318</v>
       </c>
       <c r="R6" t="n">
-        <v>6721115</v>
+        <v>6721132</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 13339-2025 artfynd.xlsx
+++ b/artfynd/A 13339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124376474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124376483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124376438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124376453</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,8 +1220,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124376501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>